--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18898238</v>
+        <v>4461232</v>
       </c>
       <c r="L2" t="n">
-        <v>11458916</v>
+        <v>2535479</v>
       </c>
       <c r="M2" t="n">
-        <v>2943400</v>
+        <v>616481</v>
       </c>
       <c r="N2" t="n">
-        <v>150121</v>
+        <v>28012</v>
       </c>
       <c r="O2" t="n">
-        <v>1744759</v>
+        <v>376347</v>
       </c>
       <c r="P2" t="n">
-        <v>693637</v>
+        <v>157132</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999342560768127</v>
+        <v>0.999937891960144</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9365973472595215</v>
+        <v>0.884272038936615</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8616405725479126</v>
+        <v>0.7613845467567444</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8304168581962585</v>
+        <v>0.698999285697937</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6062163710594177</v>
+        <v>0.3985657691955566</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8635556697845459</v>
+        <v>0.7577466368675232</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8941248059272766</v>
+        <v>0.8177399635314941</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>791</v>
+        <v>197</v>
       </c>
       <c r="D3" t="n">
-        <v>18898238</v>
+        <v>4461232</v>
       </c>
       <c r="E3" t="n">
-        <v>1207938</v>
+        <v>552700</v>
       </c>
       <c r="F3" t="n">
-        <v>15052</v>
+        <v>7776</v>
       </c>
       <c r="G3" t="n">
-        <v>2044</v>
+        <v>872</v>
       </c>
       <c r="H3" t="n">
-        <v>838</v>
+        <v>430</v>
       </c>
       <c r="I3" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>40064828</v>
+        <v>10016230</v>
       </c>
       <c r="K3" t="n">
-        <v>43914123</v>
+        <v>10722513</v>
       </c>
       <c r="L3" t="n">
-        <v>50430616</v>
+        <v>12266102</v>
       </c>
       <c r="M3" t="n">
-        <v>60989438</v>
+        <v>15131542</v>
       </c>
       <c r="N3" t="n">
-        <v>64864496</v>
+        <v>16198139</v>
       </c>
       <c r="O3" t="n">
-        <v>63006409</v>
+        <v>15699903</v>
       </c>
       <c r="P3" t="n">
-        <v>64463073</v>
+        <v>16101232</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9390444159507751</v>
+        <v>0.8881203532218933</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8782293200492859</v>
+        <v>0.7756398320198059</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7895646691322327</v>
+        <v>0.6610411405563354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4212279319763184</v>
+        <v>0.3140675723552704</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8568221926689148</v>
+        <v>0.738836407661438</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8971083760261536</v>
+        <v>0.8126984834671021</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193050064849949</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1201832</v>
+        <v>553206</v>
       </c>
       <c r="E4" t="n">
-        <v>11458916</v>
+        <v>2535479</v>
       </c>
       <c r="F4" t="n">
-        <v>358197</v>
+        <v>162378</v>
       </c>
       <c r="G4" t="n">
-        <v>8739</v>
+        <v>5104</v>
       </c>
       <c r="H4" t="n">
-        <v>18652</v>
+        <v>11753</v>
       </c>
       <c r="I4" t="n">
-        <v>1412</v>
+        <v>967</v>
       </c>
       <c r="J4" t="n">
-        <v>1660</v>
+        <v>392</v>
       </c>
       <c r="K4" t="n">
-        <v>1279310</v>
+        <v>583858</v>
       </c>
       <c r="L4" t="n">
-        <v>1840035</v>
+        <v>794611</v>
       </c>
       <c r="M4" t="n">
-        <v>601085</v>
+        <v>265467</v>
       </c>
       <c r="N4" t="n">
-        <v>97515</v>
+        <v>42270</v>
       </c>
       <c r="O4" t="n">
-        <v>275677</v>
+        <v>120319</v>
       </c>
       <c r="P4" t="n">
-        <v>82135</v>
+        <v>35022</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999671578407288</v>
+        <v>0.999968945980072</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9378193020820618</v>
+        <v>0.8861920237541199</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8698559403419495</v>
+        <v>0.7684460878372192</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8094757199287415</v>
+        <v>0.6794905066490173</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4970687925815582</v>
+        <v>0.3513070940971375</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8601757287979126</v>
+        <v>0.7481721043586731</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8956140875816345</v>
+        <v>0.8152114748954773</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>685</v>
+        <v>170</v>
       </c>
       <c r="D5" t="n">
-        <v>47251</v>
+        <v>18849</v>
       </c>
       <c r="E5" t="n">
-        <v>542600</v>
+        <v>209563</v>
       </c>
       <c r="F5" t="n">
-        <v>2943400</v>
+        <v>616481</v>
       </c>
       <c r="G5" t="n">
-        <v>40380</v>
+        <v>16977</v>
       </c>
       <c r="H5" t="n">
-        <v>145086</v>
+        <v>65459</v>
       </c>
       <c r="I5" t="n">
-        <v>8475</v>
+        <v>5092</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1226729</v>
+        <v>561997</v>
       </c>
       <c r="L5" t="n">
-        <v>1588833</v>
+        <v>733408</v>
       </c>
       <c r="M5" t="n">
-        <v>784477</v>
+        <v>316110</v>
       </c>
       <c r="N5" t="n">
-        <v>206268</v>
+        <v>61179</v>
       </c>
       <c r="O5" t="n">
-        <v>291555</v>
+        <v>133031</v>
       </c>
       <c r="P5" t="n">
-        <v>79555</v>
+        <v>36214</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999746084213257</v>
+        <v>0.9999759793281555</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9616335034370422</v>
+        <v>0.9298295974731445</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9475053548812866</v>
+        <v>0.9064264297485352</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9787875413894653</v>
+        <v>0.9643850922584534</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9953491687774658</v>
+        <v>0.9936649203300476</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9913159012794495</v>
+        <v>0.9844852089881897</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9975245594978333</v>
+        <v>0.9956375956535339</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>29978</v>
+        <v>11722</v>
       </c>
       <c r="E6" t="n">
-        <v>69355</v>
+        <v>18844</v>
       </c>
       <c r="F6" t="n">
-        <v>65685</v>
+        <v>18930</v>
       </c>
       <c r="G6" t="n">
-        <v>150121</v>
+        <v>28012</v>
       </c>
       <c r="H6" t="n">
-        <v>38519</v>
+        <v>10510</v>
       </c>
       <c r="I6" t="n">
-        <v>2596</v>
+        <v>1153</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
-        <v>19189</v>
+        <v>12900</v>
       </c>
       <c r="F7" t="n">
-        <v>158060</v>
+        <v>73880</v>
       </c>
       <c r="G7" t="n">
-        <v>44559</v>
+        <v>18410</v>
       </c>
       <c r="H7" t="n">
-        <v>1744759</v>
+        <v>376347</v>
       </c>
       <c r="I7" t="n">
-        <v>69586</v>
+        <v>27788</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>953</v>
+        <v>604</v>
       </c>
       <c r="F8" t="n">
-        <v>4091</v>
+        <v>2503</v>
       </c>
       <c r="G8" t="n">
-        <v>1793</v>
+        <v>907</v>
       </c>
       <c r="H8" t="n">
-        <v>72582</v>
+        <v>32167</v>
       </c>
       <c r="I8" t="n">
-        <v>693637</v>
+        <v>157132</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
